--- a/data/trans_orig/IMC_inf_MED_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Clase-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>28461</v>
+        <v>32724</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>22077</v>
+        <v>26007</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>34417</v>
+        <v>39663</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.4950883864855047</v>
+        <v>0.4721442466185505</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3840372459698021</v>
+        <v>0.3752321057202086</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.5986968559606604</v>
+        <v>0.5722619446107592</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>31300</v>
+        <v>34947</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>24872</v>
+        <v>27553</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>38493</v>
+        <v>41957</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4692583864642175</v>
+        <v>0.4580346939598904</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3728916188208078</v>
+        <v>0.3611300007582769</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5771130529083938</v>
+        <v>0.5499100803891388</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>59760</v>
+        <v>67671</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>50229</v>
+        <v>56974</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>68574</v>
+        <v>77493</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4812151082347214</v>
+        <v>0.4647509134375324</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4044630058641907</v>
+        <v>0.3912829008832519</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5521902307891661</v>
+        <v>0.5322049200443035</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>29025</v>
+        <v>36586</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23069</v>
+        <v>29647</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>35409</v>
+        <v>43303</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5049116135144953</v>
+        <v>0.5278557533814495</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4013031440393395</v>
+        <v>0.4277380553892407</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.615962754030198</v>
+        <v>0.6247678942797914</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>35400</v>
+        <v>41351</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>28207</v>
+        <v>34341</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>41828</v>
+        <v>48745</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5307416135357825</v>
+        <v>0.5419653060401096</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4228869470916064</v>
+        <v>0.4500899196108612</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6271083811791922</v>
+        <v>0.6388699992417232</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>64426</v>
+        <v>77937</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>55612</v>
+        <v>68115</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>73957</v>
+        <v>88634</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5187848917652786</v>
+        <v>0.5352490865624676</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4478097692108339</v>
+        <v>0.4677950799556965</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5955369941358092</v>
+        <v>0.6087170991167481</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>38393</v>
+        <v>44906</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>31199</v>
+        <v>37758</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>44422</v>
+        <v>52497</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5590002895867078</v>
+        <v>0.559713150199066</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4542515763993341</v>
+        <v>0.4706249711559162</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6467798255305163</v>
+        <v>0.654336960608853</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>28624</v>
+        <v>30120</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22205</v>
+        <v>23160</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>35624</v>
+        <v>37304</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4063203622065644</v>
+        <v>0.388490330729886</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3152085634980769</v>
+        <v>0.2987225942948434</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5056930415128734</v>
+        <v>0.4811557777313733</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>67017</v>
+        <v>75025</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>57802</v>
+        <v>64410</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>77455</v>
+        <v>84641</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4816927292635299</v>
+        <v>0.4755668064193305</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4154595807116137</v>
+        <v>0.4082797513737278</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5567191840883861</v>
+        <v>0.5365198670338697</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>30289</v>
+        <v>35324</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>24260</v>
+        <v>27733</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>37483</v>
+        <v>42472</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4409997104132923</v>
+        <v>0.440286849800934</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3532201744694846</v>
+        <v>0.345663039391147</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.545748423600666</v>
+        <v>0.5293750288440839</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>41822</v>
+        <v>47410</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>34822</v>
+        <v>40226</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>48241</v>
+        <v>54370</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5936796377934357</v>
+        <v>0.611509669270114</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4943069584871266</v>
+        <v>0.5188442222686273</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6847914365019231</v>
+        <v>0.7012774057051567</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>72111</v>
+        <v>82735</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>61673</v>
+        <v>73119</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>81326</v>
+        <v>93350</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5183072707364702</v>
+        <v>0.5244331935806695</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.443280815911614</v>
+        <v>0.4634801329661302</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.5845404192883865</v>
+        <v>0.5917202486262721</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>36156</v>
+        <v>38873</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>29985</v>
+        <v>32228</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>42453</v>
+        <v>45467</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.591495579012427</v>
+        <v>0.5745725708843314</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4905506469355158</v>
+        <v>0.4763468436957478</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6945190363597491</v>
+        <v>0.6720346684323676</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>22205</v>
+        <v>26166</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>16430</v>
+        <v>19423</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>28678</v>
+        <v>32743</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3589053252073557</v>
+        <v>0.3646165500836996</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2655544860159486</v>
+        <v>0.2706607682690913</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4635310102916321</v>
+        <v>0.4562786053170155</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>58360</v>
+        <v>65039</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>48586</v>
+        <v>55806</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>66433</v>
+        <v>75156</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.4744978398139253</v>
+        <v>0.4665027776945819</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3950298096731698</v>
+        <v>0.4002760498018049</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.5401291793147451</v>
+        <v>0.5390668244659984</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>24970</v>
+        <v>28783</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>18673</v>
+        <v>22189</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>31141</v>
+        <v>35428</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.4085044209875729</v>
+        <v>0.4254274291156686</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.305480963640251</v>
+        <v>0.3279653315676324</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.5094493530644842</v>
+        <v>0.5236531563042522</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>39664</v>
+        <v>45596</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>33191</v>
+        <v>39019</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>45439</v>
+        <v>52339</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6410946747926443</v>
+        <v>0.6353834499163004</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.536468989708368</v>
+        <v>0.5437213946829845</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7344455139840514</v>
+        <v>0.7293392317309089</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>64634</v>
+        <v>74380</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>56561</v>
+        <v>64263</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>74408</v>
+        <v>83613</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.5255021601860747</v>
+        <v>0.5334972223054181</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4598708206852549</v>
+        <v>0.4609331755340014</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6049701903268302</v>
+        <v>0.599723950198195</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>86819</v>
+        <v>99702</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>75516</v>
+        <v>88078</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>96065</v>
+        <v>111429</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5584697718743773</v>
+        <v>0.5310714897629524</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4857615266263439</v>
+        <v>0.4691529731954391</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.6179429993849284</v>
+        <v>0.5935359584627349</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>61694</v>
+        <v>72946</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>52044</v>
+        <v>63035</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>71118</v>
+        <v>83012</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4683187646268753</v>
+        <v>0.444433848002695</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3950661475911985</v>
+        <v>0.3840466812610643</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5398533414515673</v>
+        <v>0.5057628501249412</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>148514</v>
+        <v>172649</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>134576</v>
+        <v>158112</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>163946</v>
+        <v>188808</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5171176456495484</v>
+        <v>0.4906586134886743</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4685868099388488</v>
+        <v>0.4493455801527377</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5708511206834946</v>
+        <v>0.5365844204899429</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>68640</v>
+        <v>88036</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>59394</v>
+        <v>76309</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>79943</v>
+        <v>99660</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4415302281256226</v>
+        <v>0.4689285102370476</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3820570006150716</v>
+        <v>0.4064640415372651</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.5142384733736561</v>
+        <v>0.530847026804561</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>70042</v>
+        <v>91187</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>60618</v>
+        <v>81121</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>79692</v>
+        <v>101098</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5316812353731247</v>
+        <v>0.555566151997305</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4601466585484326</v>
+        <v>0.4942371498750591</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6049338524088014</v>
+        <v>0.615953318738936</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>138681</v>
+        <v>179222</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>123249</v>
+        <v>163063</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>152619</v>
+        <v>193759</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.4828823543504515</v>
+        <v>0.5093413865113257</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4291488793165055</v>
+        <v>0.463415579510057</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.5314131900611513</v>
+        <v>0.5506544198472617</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>413</v>
+        <v>506</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>48443</v>
+        <v>59576</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>39910</v>
+        <v>50737</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>56002</v>
+        <v>69553</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4910130155199303</v>
+        <v>0.4826667076753454</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4045274292161258</v>
+        <v>0.41105587790296</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5676270840803367</v>
+        <v>0.5635023269474246</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>54416</v>
+        <v>67559</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>46215</v>
+        <v>57933</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>62518</v>
+        <v>77101</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5014592777442417</v>
+        <v>0.5197316425220008</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.4258892205550592</v>
+        <v>0.4456767616719172</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5761201633934706</v>
+        <v>0.5931428118172647</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>102859</v>
+        <v>127134</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>90444</v>
+        <v>113620</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>114791</v>
+        <v>139453</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4964846494584426</v>
+        <v>0.5016787977957564</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.436558792902818</v>
+        <v>0.4483486864315634</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5540801786217485</v>
+        <v>0.5502900229502886</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>50216</v>
+        <v>63854</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>42657</v>
+        <v>53877</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>58749</v>
+        <v>72693</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5089869844800697</v>
+        <v>0.5173332923246546</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4323729159196633</v>
+        <v>0.4364976730525754</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5954725707838741</v>
+        <v>0.5889441220970396</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>54099</v>
+        <v>62429</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>45997</v>
+        <v>52887</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>62300</v>
+        <v>72055</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4985407222557583</v>
+        <v>0.4802683574779992</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.4238798366065294</v>
+        <v>0.4068571881827353</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5741107794449408</v>
+        <v>0.5543232383280824</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>104315</v>
+        <v>126284</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>92383</v>
+        <v>113965</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>116730</v>
+        <v>139798</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5035153505415574</v>
+        <v>0.4983212022042436</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4459198213782515</v>
+        <v>0.4497099770497113</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.5634412070971819</v>
+        <v>0.5516513135684366</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1814,67 +1814,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>29305</v>
+        <v>33566</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>23459</v>
+        <v>26723</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>35227</v>
+        <v>39893</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.5421267841278568</v>
+        <v>0.5347298651216033</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.433976573721105</v>
+        <v>0.4257251139973388</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6516770726052458</v>
+        <v>0.6355317523540791</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>20876</v>
+        <v>24104</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15419</v>
+        <v>18159</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>26102</v>
+        <v>29674</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5094849537715198</v>
+        <v>0.535774939050665</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3763004831438864</v>
+        <v>0.4036308893530841</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6370391861613081</v>
+        <v>0.6595905664495053</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>50181</v>
+        <v>57670</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>42101</v>
+        <v>49795</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>58660</v>
+        <v>66218</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5280526257689994</v>
+        <v>0.5351661777304914</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4430266725256092</v>
+        <v>0.462089231767097</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6172751970647706</v>
+        <v>0.6144928095158084</v>
       </c>
     </row>
     <row r="20">
@@ -1885,67 +1885,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>24751</v>
+        <v>29205</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>18829</v>
+        <v>22878</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>30597</v>
+        <v>36048</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4578732158721432</v>
+        <v>0.4652701348783967</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.3483229273947543</v>
+        <v>0.3644682476459209</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.5660234262788951</v>
+        <v>0.5742748860026612</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>20098</v>
+        <v>20885</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>14872</v>
+        <v>15315</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>25555</v>
+        <v>26830</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.4905150462284801</v>
+        <v>0.464225060949335</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3629608138386921</v>
+        <v>0.3404094335504947</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.6236995168561135</v>
+        <v>0.5963691106469159</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>44850</v>
+        <v>50090</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>36371</v>
+        <v>41542</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>52930</v>
+        <v>57965</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.4719473742310006</v>
+        <v>0.4648338222695086</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.3827248029352293</v>
+        <v>0.3855071904841915</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.5569733274743908</v>
+        <v>0.5379107682329028</v>
       </c>
     </row>
     <row r="21">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1977,16 +1977,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1998,16 +1998,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2031,67 +2031,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>267577</v>
+        <v>309347</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>247548</v>
+        <v>290381</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>286405</v>
+        <v>331390</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.5400487697576704</v>
+        <v>0.5233098709991656</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4996251285875951</v>
+        <v>0.4912254032521671</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.5780499329764833</v>
+        <v>0.5605990219570122</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>219114</v>
+        <v>255842</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>200931</v>
+        <v>236791</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>238290</v>
+        <v>274640</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.4562600371017859</v>
+        <v>0.4530573722418574</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.4183969623217635</v>
+        <v>0.4193201577281759</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.4961899191565701</v>
+        <v>0.4863457808887923</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>698</v>
+        <v>807</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>486691</v>
+        <v>565189</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>462280</v>
+        <v>537471</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>513733</v>
+        <v>591084</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.49880823141631</v>
+        <v>0.4889869467106718</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.4737892057387402</v>
+        <v>0.4650060060091347</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.526522940532226</v>
+        <v>0.5113904973995648</v>
       </c>
     </row>
     <row r="23">
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>227891</v>
+        <v>281788</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>209063</v>
+        <v>259745</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>247920</v>
+        <v>300754</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.4599512302423296</v>
+        <v>0.4766901290008344</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.4219500670235167</v>
+        <v>0.4394009780429879</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.5003748714124051</v>
+        <v>0.508774596747833</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>261126</v>
+        <v>308859</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>241950</v>
+        <v>290061</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>279309</v>
+        <v>327910</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.5437399628982141</v>
+        <v>0.5469426277581426</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.5038100808434299</v>
+        <v>0.5136542191112078</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.5816030376782366</v>
+        <v>0.580679842271824</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>703</v>
+        <v>852</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>489017</v>
+        <v>590647</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>461975</v>
+        <v>564752</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>513428</v>
+        <v>618365</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.5011917685836901</v>
+        <v>0.5110130532893282</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.4734770594677739</v>
+        <v>0.4886095026004352</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.5262107942612597</v>
+        <v>0.5349939939908652</v>
       </c>
     </row>
     <row r="24">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>712</v>
+        <v>848</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>689</v>
+        <v>811</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -2215,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>1401</v>
+        <v>1659</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -2298,7 +2298,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2482,67 +2482,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>30054</v>
+        <v>34243</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>23502</v>
+        <v>27016</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>36097</v>
+        <v>41199</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.4639644431789868</v>
+        <v>0.4304205301952377</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3628175528688306</v>
+        <v>0.3395842972910213</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.5572461660287884</v>
+        <v>0.5178657618593735</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>18743</v>
+        <v>22344</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13050</v>
+        <v>17271</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>25244</v>
+        <v>29152</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3523770343304312</v>
+        <v>0.353590731538705</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2453493091855998</v>
+        <v>0.2733175632059021</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4746060265813586</v>
+        <v>0.4613178463794927</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>48797</v>
+        <v>56586</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>40660</v>
+        <v>47492</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>57578</v>
+        <v>65965</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4136515777078792</v>
+        <v>0.3964094388068007</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3446736677530739</v>
+        <v>0.3326990214290708</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.4880898067108342</v>
+        <v>0.4621082008649425</v>
       </c>
     </row>
     <row r="5">
@@ -2553,67 +2553,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>34723</v>
+        <v>45313</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>28680</v>
+        <v>38357</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>41275</v>
+        <v>52540</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5360355568210132</v>
+        <v>0.5695794698047623</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4427538339712116</v>
+        <v>0.4821342381406264</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6371824471311694</v>
+        <v>0.6604157027089786</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>34446</v>
+        <v>40848</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>27945</v>
+        <v>34040</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>40139</v>
+        <v>45921</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6476229656695688</v>
+        <v>0.6464092684612951</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5253939734186414</v>
+        <v>0.5386821536205072</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7546506908144001</v>
+        <v>0.7266824367940979</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>69169</v>
+        <v>86161</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>60388</v>
+        <v>76782</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>77306</v>
+        <v>95255</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5863484222921208</v>
+        <v>0.6035905611931992</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.5119101932891659</v>
+        <v>0.5378917991350574</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6553263322469265</v>
+        <v>0.6673009785709291</v>
       </c>
     </row>
     <row r="6">
@@ -2624,16 +2624,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2645,16 +2645,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2666,16 +2666,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2699,67 +2699,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>30585</v>
+        <v>36381</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>23957</v>
+        <v>28924</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>37826</v>
+        <v>43654</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3704225963839458</v>
+        <v>0.3848055374642713</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2901527784880316</v>
+        <v>0.3059264484731631</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.4581193354382067</v>
+        <v>0.4617275054457644</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>14270</v>
+        <v>16922</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>9818</v>
+        <v>12140</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>21265</v>
+        <v>23403</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2042574839303282</v>
+        <v>0.2045038615577777</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1405360730381515</v>
+        <v>0.1467104030108419</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3043848704956998</v>
+        <v>0.2828191784241611</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>44855</v>
+        <v>53303</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>36175</v>
+        <v>43820</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>53530</v>
+        <v>63515</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2942645838876849</v>
+        <v>0.3006524073840594</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2373247317076111</v>
+        <v>0.2471612028863786</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.3511766592815423</v>
+        <v>0.3582487205889957</v>
       </c>
     </row>
     <row r="8">
@@ -2770,67 +2770,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>51982</v>
+        <v>58163</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>44741</v>
+        <v>50890</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>58610</v>
+        <v>65620</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6295774036160542</v>
+        <v>0.6151944625357286</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5418806645617936</v>
+        <v>0.5382724945542356</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7098472215119686</v>
+        <v>0.6940735515268369</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>55593</v>
+        <v>65826</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>48598</v>
+        <v>59345</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>60045</v>
+        <v>70608</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7957425160696718</v>
+        <v>0.7954961384422222</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6956151295043004</v>
+        <v>0.7171808215758392</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8594639269618487</v>
+        <v>0.8532895969891581</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>107575</v>
+        <v>123989</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>98900</v>
+        <v>113777</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>116255</v>
+        <v>133472</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7057354161123152</v>
+        <v>0.6993475926159406</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.6488233407184577</v>
+        <v>0.641751279411004</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7626752682923889</v>
+        <v>0.7528387971136207</v>
       </c>
     </row>
     <row r="9">
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2862,16 +2862,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2883,16 +2883,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2916,67 +2916,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>26607</v>
+        <v>31211</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>20514</v>
+        <v>24683</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>33181</v>
+        <v>37085</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4653391616987546</v>
+        <v>0.4837770867891391</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3587806094213637</v>
+        <v>0.3825968564232778</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5803050449002165</v>
+        <v>0.5748328126035832</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>14138</v>
+        <v>16017</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>9565</v>
+        <v>11165</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>20866</v>
+        <v>21748</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3090309998018835</v>
+        <v>0.303439267428426</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2090622177653788</v>
+        <v>0.2115312234679032</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4560854585002428</v>
+        <v>0.4120143514358514</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>40745</v>
+        <v>47228</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>32718</v>
+        <v>39543</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>48735</v>
+        <v>55419</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3958627426121197</v>
+        <v>0.4026260834607225</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3178724256526423</v>
+        <v>0.3371147219032791</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4734815222733221</v>
+        <v>0.4724594939405639</v>
       </c>
     </row>
     <row r="11">
@@ -2987,67 +2987,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>30571</v>
+        <v>33304</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>23997</v>
+        <v>27430</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>36664</v>
+        <v>39832</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5346608383012454</v>
+        <v>0.5162229132108609</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4196949550997839</v>
+        <v>0.4251671873964168</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6412193905786362</v>
+        <v>0.6174031435767222</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>31612</v>
+        <v>36767</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>24884</v>
+        <v>31036</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>36185</v>
+        <v>41619</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6909690001981165</v>
+        <v>0.696560732571574</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.543914541499757</v>
+        <v>0.5879856485641488</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7909377822346212</v>
+        <v>0.7884687765320969</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>62183</v>
+        <v>70071</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>54193</v>
+        <v>61880</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>70210</v>
+        <v>77756</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6041372573878803</v>
+        <v>0.5973739165392775</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5265184777266779</v>
+        <v>0.527540506059436</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6821275743473577</v>
+        <v>0.6628852780967208</v>
       </c>
     </row>
     <row r="12">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3079,16 +3079,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3100,16 +3100,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3133,67 +3133,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>64320</v>
+        <v>84136</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>54796</v>
+        <v>73568</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>74281</v>
+        <v>94927</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4444876983695238</v>
+        <v>0.4631839175595278</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3786733518658981</v>
+        <v>0.4050025970356094</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5133238128750438</v>
+        <v>0.5225932511533984</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>60341</v>
+        <v>68705</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>50523</v>
+        <v>58121</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>70684</v>
+        <v>79214</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4004334649311307</v>
+        <v>0.3817540551331107</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3352785339405721</v>
+        <v>0.3229425256679995</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4690746645258742</v>
+        <v>0.4401437628459973</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>124661</v>
+        <v>152841</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>110936</v>
+        <v>136707</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>138748</v>
+        <v>169543</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4220144563765982</v>
+        <v>0.4226575232880182</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3755504989645277</v>
+        <v>0.3780404565361764</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.469702838089411</v>
+        <v>0.4688451983202978</v>
       </c>
     </row>
     <row r="14">
@@ -3204,67 +3204,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>80386</v>
+        <v>97511</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>70425</v>
+        <v>86720</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>89910</v>
+        <v>108079</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5555123016304763</v>
+        <v>0.5368160824404723</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4866761871249562</v>
+        <v>0.4774067488466014</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6213266481341018</v>
+        <v>0.5949974029643905</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>90348</v>
+        <v>111267</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>80005</v>
+        <v>100758</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>100166</v>
+        <v>121851</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5995665350688693</v>
+        <v>0.6182459448668893</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5309253354741262</v>
+        <v>0.5598562371540027</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6647214660594282</v>
+        <v>0.6770574743320005</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>251</v>
+        <v>306</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>170734</v>
+        <v>208778</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>156647</v>
+        <v>192076</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>184459</v>
+        <v>224912</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5779855436234018</v>
+        <v>0.5773424767119818</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.530297161910589</v>
+        <v>0.5311548016797023</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6244495010354721</v>
+        <v>0.6219595434638236</v>
       </c>
     </row>
     <row r="15">
@@ -3275,16 +3275,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3296,16 +3296,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3317,16 +3317,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>433</v>
+        <v>529</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3350,67 +3350,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>54150</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>45153</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>63768</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.4378340109592818</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.3650877346221329</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.5155951061446589</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>48167</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>39704</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>57079</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.4765048001115075</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.3927831132638092</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.5646684471660797</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>52</v>
-      </c>
       <c r="K16" s="5" t="n">
-        <v>35026</v>
+        <v>43881</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>27615</v>
+        <v>35173</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>43567</v>
+        <v>53057</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3596532192327975</v>
+        <v>0.3651431337152672</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2835504861778964</v>
+        <v>0.2926832046843554</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4473522039700121</v>
+        <v>0.4415047820917247</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>83193</v>
+        <v>98031</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>71411</v>
+        <v>85089</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>94328</v>
+        <v>111338</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.419166701450722</v>
+        <v>0.4020109509193902</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.359801715452724</v>
+        <v>0.3489380175803993</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.4752696819868266</v>
+        <v>0.4565807861168629</v>
       </c>
     </row>
     <row r="17">
@@ -3421,67 +3421,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>52917</v>
+        <v>69528</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>44005</v>
+        <v>59910</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>61380</v>
+        <v>78525</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5234951998884925</v>
+        <v>0.5621659890407182</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4353315528339207</v>
+        <v>0.4844048938553411</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6072168867361909</v>
+        <v>0.6349122653778666</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>62363</v>
+        <v>76293</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>53822</v>
+        <v>67117</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>69774</v>
+        <v>85001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6403467807672024</v>
+        <v>0.6348568662847328</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5526477960299881</v>
+        <v>0.5584952179082755</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.7164495138221036</v>
+        <v>0.7073167953156446</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>115279</v>
+        <v>145821</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>104144</v>
+        <v>132514</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>127061</v>
+        <v>158763</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.580833298549278</v>
+        <v>0.5979890490806099</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.5247303180131734</v>
+        <v>0.5434192138831371</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6401982845472759</v>
+        <v>0.6510619824196007</v>
       </c>
     </row>
     <row r="18">
@@ -3492,16 +3492,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3513,16 +3513,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3534,16 +3534,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3567,67 +3567,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24577</v>
+        <v>28097</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>18422</v>
+        <v>22082</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>30918</v>
+        <v>34452</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.488540548106995</v>
+        <v>0.4819565507956208</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3661925979531799</v>
+        <v>0.3787798351419578</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6145893210880495</v>
+        <v>0.5909578056093808</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>17233</v>
+        <v>17868</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>12099</v>
+        <v>12974</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>22860</v>
+        <v>23836</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3939503461214214</v>
+        <v>0.3675177166003735</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.276600615386649</v>
+        <v>0.2668499346554004</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.5225964454344277</v>
+        <v>0.4902539443870248</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>41810</v>
+        <v>45966</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>34727</v>
+        <v>37447</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>50211</v>
+        <v>54741</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.4445459004366074</v>
+        <v>0.4299168654940712</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.3692421507988616</v>
+        <v>0.3502414052974245</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5338791474816577</v>
+        <v>0.5119929718795039</v>
       </c>
     </row>
     <row r="20">
@@ -3638,67 +3638,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>25729</v>
+        <v>30201</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>19388</v>
+        <v>23846</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31884</v>
+        <v>36216</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.5114594518930049</v>
+        <v>0.5180434492043792</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.3854106789119505</v>
+        <v>0.4090421943906192</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.6338074020468201</v>
+        <v>0.6212201648580421</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>26510</v>
+        <v>30751</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>20883</v>
+        <v>24783</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>31644</v>
+        <v>35645</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.6060496538785786</v>
+        <v>0.6324822833996265</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4774035545655725</v>
+        <v>0.509746055612975</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.7233993846133512</v>
+        <v>0.7331500653445996</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>52240</v>
+        <v>60952</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>43839</v>
+        <v>52177</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>59323</v>
+        <v>69471</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.5554540995633926</v>
+        <v>0.5700831345059288</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.4661208525183425</v>
+        <v>0.4880070281204958</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.6307578492011384</v>
+        <v>0.6497585947025754</v>
       </c>
     </row>
     <row r="21">
@@ -3709,37 +3709,37 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>63</v>
-      </c>
       <c r="K21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -3751,16 +3751,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -3784,67 +3784,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>224310</v>
+        <v>268218</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>205594</v>
+        <v>245012</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>243178</v>
+        <v>287321</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4480654188894941</v>
+        <v>0.4453687980742428</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4106805262273104</v>
+        <v>0.4068366658119761</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4857564590195868</v>
+        <v>0.4770889245991267</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>159750</v>
+        <v>185737</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>143382</v>
+        <v>168131</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>176748</v>
+        <v>204629</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.3468140949919547</v>
+        <v>0.3392528142213509</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3112787372634779</v>
+        <v>0.3070953334356151</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3837152213913932</v>
+        <v>0.3737586846368712</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>558</v>
+        <v>661</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>384060</v>
+        <v>453955</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>359557</v>
+        <v>423764</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>407260</v>
+        <v>480828</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.3995462405159839</v>
+        <v>0.394837364808361</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.374054728858</v>
+        <v>0.368577974390697</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.4236813438132241</v>
+        <v>0.4182105055239382</v>
       </c>
     </row>
     <row r="23">
@@ -3855,67 +3855,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>393</v>
+        <v>474</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>276308</v>
+        <v>334020</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>257440</v>
+        <v>314917</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>295024</v>
+        <v>357226</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.5519345811105059</v>
+        <v>0.5546312019257572</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.5142435409804132</v>
+        <v>0.5229110754008732</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.5893194737726895</v>
+        <v>0.5931633341880237</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>450</v>
+        <v>542</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>300872</v>
+        <v>361752</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>283874</v>
+        <v>342860</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>317240</v>
+        <v>379358</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.6531859050080453</v>
+        <v>0.6607471857786491</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.616284778608607</v>
+        <v>0.6262413153631289</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.6887212627365226</v>
+        <v>0.6929046665643849</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>843</v>
+        <v>1016</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>577181</v>
+        <v>695772</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>553981</v>
+        <v>668899</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>601684</v>
+        <v>725963</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.6004537594840161</v>
+        <v>0.605162635191639</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.5763186561867758</v>
+        <v>0.5817894944760619</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.625945271142</v>
+        <v>0.6314220256093035</v>
       </c>
     </row>
     <row r="24">
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>713</v>
+        <v>857</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -3947,16 +3947,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>688</v>
+        <v>820</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -3968,16 +3968,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>1401</v>
+        <v>1677</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -4051,7 +4051,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4235,25 +4235,25 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13090</v>
+        <v>14553</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7736</v>
+        <v>9105</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18943</v>
+        <v>21073</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2453074725274109</v>
+        <v>0.2601939043262253</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1449736602885894</v>
+        <v>0.1628013394600248</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3550101786153673</v>
+        <v>0.376780566758476</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>17</v>
@@ -4262,40 +4262,40 @@
         <v>12069</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>7734</v>
+        <v>7449</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>18205</v>
+        <v>17727</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3040719973745114</v>
+        <v>0.2975963636105182</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1948606299224274</v>
+        <v>0.1836762250542637</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4586747190938486</v>
+        <v>0.4371136232166608</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>25159</v>
+        <v>26622</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>18514</v>
+        <v>19600</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>32966</v>
+        <v>34204</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2703736689877505</v>
+        <v>0.2759150132596055</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1989621966833351</v>
+        <v>0.20313713730636</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3542774033438456</v>
+        <v>0.3544961867796946</v>
       </c>
     </row>
     <row r="5">
@@ -4306,67 +4306,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>40270</v>
+        <v>41377</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>34417</v>
+        <v>34857</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>45624</v>
+        <v>46825</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7546925274725891</v>
+        <v>0.7398060956737748</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6449898213846335</v>
+        <v>0.623219433241524</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8550263397114107</v>
+        <v>0.837198660539975</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>27622</v>
+        <v>28486</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>21486</v>
+        <v>22828</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>31957</v>
+        <v>33106</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6959280026254885</v>
+        <v>0.7024036363894816</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5413252809061513</v>
+        <v>0.5628863767833393</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8051393700775725</v>
+        <v>0.8163237749457368</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>67892</v>
+        <v>69863</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>60085</v>
+        <v>62281</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>74537</v>
+        <v>76885</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7296263310122495</v>
+        <v>0.7240849867403945</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6457225966561544</v>
+        <v>0.6455038132203057</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8010378033166647</v>
+        <v>0.7968628626936399</v>
       </c>
     </row>
     <row r="6">
@@ -4377,16 +4377,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -4398,16 +4398,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -4419,16 +4419,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -4458,19 +4458,19 @@
         <v>17853</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11975</v>
+        <v>11989</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>23419</v>
+        <v>23826</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4279946886298591</v>
+        <v>0.4215147042495658</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2870792971612113</v>
+        <v>0.2830651067350457</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.561439150312588</v>
+        <v>0.5625503182566621</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>15</v>
@@ -4479,40 +4479,40 @@
         <v>9047</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>5354</v>
+        <v>5357</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>13860</v>
+        <v>14212</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2261622792098627</v>
+        <v>0.2114367487059814</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1338349014798279</v>
+        <v>0.1251979111660162</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3464868863215999</v>
+        <v>0.3321608056964345</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>39</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>26900</v>
+        <v>26899</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>20177</v>
+        <v>20174</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>34728</v>
+        <v>35299</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3291913144812575</v>
+        <v>0.3159404689891355</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2469254781142139</v>
+        <v>0.2369526875369</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4249957781046009</v>
+        <v>0.4145942944219099</v>
       </c>
     </row>
     <row r="8">
@@ -4523,67 +4523,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>23859</v>
+        <v>24501</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>18293</v>
+        <v>18528</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>29737</v>
+        <v>30365</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5720053113701407</v>
+        <v>0.5784852957504343</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4385608496874119</v>
+        <v>0.437449681743338</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7129207028387886</v>
+        <v>0.7169348932649543</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>30955</v>
+        <v>33740</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>26142</v>
+        <v>28575</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>34648</v>
+        <v>37430</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7738377207901374</v>
+        <v>0.7885632512940185</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6535131136783998</v>
+        <v>0.6678391943035655</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8661650985201713</v>
+        <v>0.8748020888339838</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>54814</v>
+        <v>58242</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>46986</v>
+        <v>49842</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>61537</v>
+        <v>64967</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6708086855187425</v>
+        <v>0.6840595310108645</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5750042218953988</v>
+        <v>0.5854057055780901</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7530745218857863</v>
+        <v>0.7630473124631</v>
       </c>
     </row>
     <row r="9">
@@ -4594,16 +4594,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -4615,16 +4615,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -4636,16 +4636,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -4672,64 +4672,64 @@
         <v>18</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>12834</v>
+        <v>12835</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>8649</v>
+        <v>8588</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17291</v>
+        <v>17815</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4631545786922261</v>
+        <v>0.4376798603237079</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3121131133812513</v>
+        <v>0.2928628716238596</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6239847784174877</v>
+        <v>0.6075339020399102</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>3927</v>
+        <v>4802</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1658</v>
+        <v>2248</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>7700</v>
+        <v>8521</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2300828967869636</v>
+        <v>0.2459987332216569</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.09712291400918706</v>
+        <v>0.1151717948020793</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4511487328328252</v>
+        <v>0.4364910881804661</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>16762</v>
+        <v>17637</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>11879</v>
+        <v>12567</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>23218</v>
+        <v>23931</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3743162207524371</v>
+        <v>0.361072812573408</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2652872950474532</v>
+        <v>0.2572728656021662</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.5185043300132467</v>
+        <v>0.4899271227258086</v>
       </c>
     </row>
     <row r="11">
@@ -4740,67 +4740,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>14877</v>
+        <v>16489</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>10420</v>
+        <v>11509</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>19062</v>
+        <v>20736</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5368454213077738</v>
+        <v>0.5623201396762919</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.3760152215825121</v>
+        <v>0.3924660979600899</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6878868866187489</v>
+        <v>0.7071371283761404</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>13141</v>
+        <v>14720</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>9368</v>
+        <v>11001</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>15410</v>
+        <v>17274</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7699171032130365</v>
+        <v>0.7540012667783432</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.548851267167175</v>
+        <v>0.5635089118195337</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9028770859908131</v>
+        <v>0.8848282051979206</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>28017</v>
+        <v>31209</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>21561</v>
+        <v>24915</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>32900</v>
+        <v>36279</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6256837792475627</v>
+        <v>0.6389271874265919</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4814956699867531</v>
+        <v>0.5100728772741911</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7347127049525467</v>
+        <v>0.7427271343978338</v>
       </c>
     </row>
     <row r="12">
@@ -4811,16 +4811,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -4832,16 +4832,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -4853,16 +4853,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4886,67 +4886,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>34512</v>
+        <v>36775</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>26165</v>
+        <v>27653</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>44450</v>
+        <v>46217</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4320796174583575</v>
+        <v>0.4343958513270552</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3275827814169261</v>
+        <v>0.32664695444081</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5565059936902863</v>
+        <v>0.5459380059827279</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>21123</v>
+        <v>21948</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>15301</v>
+        <v>15920</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>27853</v>
+        <v>29159</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2821802332829729</v>
+        <v>0.2854064585885532</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2044035554264337</v>
+        <v>0.2070222714906544</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3720904634689053</v>
+        <v>0.3791765803161776</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>55635</v>
+        <v>58723</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>44659</v>
+        <v>48719</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>67226</v>
+        <v>72048</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3595605918357767</v>
+        <v>0.3634770817561652</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2886232154613662</v>
+        <v>0.3015514534420772</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4344748816158981</v>
+        <v>0.4459530920797139</v>
       </c>
     </row>
     <row r="14">
@@ -4957,67 +4957,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>45362</v>
+        <v>47882</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>35424</v>
+        <v>38440</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>53709</v>
+        <v>57004</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5679203825416425</v>
+        <v>0.565604148672945</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4434940063097138</v>
+        <v>0.4540619940172724</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6724172185830739</v>
+        <v>0.6733530455591901</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>53733</v>
+        <v>54954</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>47003</v>
+        <v>47743</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>59555</v>
+        <v>60982</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7178197667170271</v>
+        <v>0.7145935414114466</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6279095365310949</v>
+        <v>0.6208234196838222</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7955964445735665</v>
+        <v>0.7929777285093457</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>99095</v>
+        <v>102837</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>87504</v>
+        <v>89512</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>110071</v>
+        <v>112841</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6404394081642234</v>
+        <v>0.6365229182438347</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.5655251183841018</v>
+        <v>0.554046907920286</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7113767845386334</v>
+        <v>0.6984485465579225</v>
       </c>
     </row>
     <row r="15">
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -5049,16 +5049,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -5070,16 +5070,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -5103,67 +5103,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>24826</v>
+        <v>27046</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>19181</v>
+        <v>20478</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>30935</v>
+        <v>34040</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4669439987729551</v>
+        <v>0.4649596684071307</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3607651473145992</v>
+        <v>0.3520446061602461</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5818362417338362</v>
+        <v>0.5851856702461377</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>15908</v>
+        <v>19608</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>11645</v>
+        <v>14331</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>20775</v>
+        <v>24357</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4656997393117255</v>
+        <v>0.5101755015521316</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3409191867544041</v>
+        <v>0.3728904041898268</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.6081889663860621</v>
+        <v>0.6337528628089223</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>40735</v>
+        <v>46654</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>33119</v>
+        <v>38174</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>48728</v>
+        <v>54993</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4664572925398638</v>
+        <v>0.482948875218793</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3792477430009398</v>
+        <v>0.3951691586050876</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5579891800564738</v>
+        <v>0.5692781317268175</v>
       </c>
     </row>
     <row r="17">
@@ -5174,67 +5174,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>28342</v>
+        <v>31123</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>22233</v>
+        <v>24129</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>33987</v>
+        <v>37691</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5330560012270449</v>
+        <v>0.5350403315928693</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4181637582661638</v>
+        <v>0.4148143297538624</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6392348526854007</v>
+        <v>0.647955393839754</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>18251</v>
+        <v>18825</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>13384</v>
+        <v>14076</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>22514</v>
+        <v>24102</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5343002606882745</v>
+        <v>0.4898244984478684</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3918110336139378</v>
+        <v>0.3662471371910778</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.6590808132455958</v>
+        <v>0.6271095958101732</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>46593</v>
+        <v>49948</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>38600</v>
+        <v>41609</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>54209</v>
+        <v>58428</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5335427074601362</v>
+        <v>0.5170511247812071</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4420108199435265</v>
+        <v>0.4307218682731821</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6207522569990602</v>
+        <v>0.6048308413949123</v>
       </c>
     </row>
     <row r="18">
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -5266,16 +5266,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -5287,16 +5287,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -5537,67 +5537,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>118309</v>
+        <v>124255</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>102253</v>
+        <v>109267</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>133619</v>
+        <v>140275</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4081513143855126</v>
+        <v>0.4080958190249358</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3527606620784921</v>
+        <v>0.3588727287621079</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4609695998547796</v>
+        <v>0.4607130629950928</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>65679</v>
+        <v>71080</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>53618</v>
+        <v>60322</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>76793</v>
+        <v>83707</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2819354703247623</v>
+        <v>0.2896701426666734</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2301624121584185</v>
+        <v>0.2458290466998841</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3296438253972433</v>
+        <v>0.3411294923580518</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>183988</v>
+        <v>195334</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>165391</v>
+        <v>176471</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>205961</v>
+        <v>216491</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.3519124556250235</v>
+        <v>0.3552465402686676</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.3163417680633482</v>
+        <v>0.3209409335061819</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.3939399839100733</v>
+        <v>0.3937233960810387</v>
       </c>
     </row>
     <row r="23">
@@ -5608,67 +5608,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>171556</v>
+        <v>180219</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>156246</v>
+        <v>164199</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>187612</v>
+        <v>195207</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.5918486856144874</v>
+        <v>0.5919041809750643</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.5390304001452205</v>
+        <v>0.5392869370049072</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.647239337921508</v>
+        <v>0.6411272712378923</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>167279</v>
+        <v>174301</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>156165</v>
+        <v>161674</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>179340</v>
+        <v>185059</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.7180645296752377</v>
+        <v>0.7103298573333267</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.6703561746027562</v>
+        <v>0.6588705076419481</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.7698375878415814</v>
+        <v>0.7541709533001159</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>338835</v>
+        <v>354521</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>316862</v>
+        <v>333364</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>357432</v>
+        <v>373384</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.6480875443749765</v>
+        <v>0.6447534597313324</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.6060600160899268</v>
+        <v>0.6062766039189613</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.6836582319366517</v>
+        <v>0.6790590664938181</v>
       </c>
     </row>
     <row r="24">
@@ -5679,16 +5679,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -5700,16 +5700,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -5721,16 +5721,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>753</v>
+        <v>792</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
